--- a/PTBR-COM-PORTRAIT/Lang/PTBR/Dialog/Drama/corgon.xlsx
+++ b/PTBR-COM-PORTRAIT/Lang/PTBR/Dialog/Drama/corgon.xlsx
@@ -451,7 +451,7 @@
           <t>(mokyu?)</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L8" s="8" t="inlineStr">
         <is>
           <t>(mokyu?)</t>
         </is>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="L46" s="11" t="inlineStr">
         <is>
-          <t>Para teste</t>
+          <t>Para teste.</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="L52" s="11" t="inlineStr">
         <is>
-          <t>Para teste</t>
+          <t>Para teste.</t>
         </is>
       </c>
     </row>
